--- a/incident_report_forms/032_retail_store_incident_form--incident_report_forms.xlsx
+++ b/incident_report_forms/032_retail_store_incident_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,14 +525,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Incident Date</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Date of the incident</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -552,14 +548,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Incident Time</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Time of the incident</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -579,14 +571,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Incident Type</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Type of incident</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -606,14 +594,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Incident Location</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Location of the incident</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -633,14 +617,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Incident Description</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Incident description</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -650,27 +630,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>incident_status</t>
+          <t>incident_category</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Incident Status</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Incident category</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -687,14 +663,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Retail Store ID</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Retail store ID</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,78 +676,66 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>incident_category</t>
+          <t>incident_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Incident Category</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Incident status</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>employee_id</t>
+          <t>incident_reported_by</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Incident reported by</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>incident_reported_by</t>
+          <t>incident_reported_by_email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Incident Reported By</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Incident reported by email</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -790,19 +750,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>incident_reported_by_email</t>
+          <t>incident_reported_by_phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Incident Reported By Email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Incident reported by phone</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -817,323 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>incident_reported_by_phone</t>
+          <t>employee_id</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Incident Reported By Phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Employee ID</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>employee_id</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>incident_status</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Incident Status</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>incident_type</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Incident Type</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>incident_date</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Incident Date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>incident_time</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Incident Time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>incident_location</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Incident Location</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>incident_description</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Incident Description</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>incident_category</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Incident Category</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>retail_store_id</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Retail Store ID</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>employee_id</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Employee ID</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>incident_reported_by</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Incident Reported By</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>incident_reported_by_email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Incident Reported By Email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>incident_reported_by_phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Incident Reported By Phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1150,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1183,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_'incident_type',_'label':_'null'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 'Incident Type', 'label': 'null'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1200,80 +849,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_'other',_'label':_'other'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 'Other', 'label': 'Other'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>incident_status_choices</t>
+          <t>incident_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option1':_'active',_'label':_'null'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option1': 'Active', 'label': 'null'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>incident_status_choices</t>
+          <t>incident_category_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option2':_'inactive',_'label':_'null'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option2': 'Inactive', 'label': 'null'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>incident_status_choices</t>
+          <t>incident_category_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option3':_'pending',_'label':_'null'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option3': 'Pending', 'label': 'null'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>retail_store_id_choices</t>
+          <t>incident_category_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option1':_'retail_store_1',_'label':_'null'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option1': 'Retail Store 1', 'label': 'null'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
@@ -1285,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option2':_'retail_store_2',_'label':_'null'}</t>
+          <t>retail_store_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option2': 'Retail Store 2', 'label': 'null'}</t>
+          <t>Retail Store 1</t>
         </is>
       </c>
     </row>
@@ -1302,80 +951,80 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option3':_'retail_store_3',_'label':_'null'}</t>
+          <t>retail_store_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option3': 'Retail Store 3', 'label': 'null'}</t>
+          <t>Retail Store 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>incident_category_choices</t>
+          <t>retail_store_id_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option1':_'category_1',_'label':_'null'}</t>
+          <t>retail_store_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option1': 'Category 1', 'label': 'null'}</t>
+          <t>Retail Store 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>incident_category_choices</t>
+          <t>incident_status_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option2':_'category_2',_'label':_'null'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option2': 'Category 2', 'label': 'null'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>incident_category_choices</t>
+          <t>incident_status_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option3':_'category_3',_'label':_'null'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option3': 'Category 3', 'label': 'null'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>incident_reported_by_choices</t>
+          <t>incident_status_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option1':_'employee_1',_'label':_'null'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option1': 'Employee 1', 'label': 'null'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option2':_'employee_2',_'label':_'null'}</t>
+          <t>employee_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option2': 'Employee 2', 'label': 'null'}</t>
+          <t>Employee 1</t>
         </is>
       </c>
     </row>
@@ -1404,250 +1053,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option3':_'employee_3',_'label':_'null'}</t>
+          <t>employee_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option3': 'Employee 3', 'label': 'null'}</t>
+          <t>Employee 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>incident_status_choices</t>
+          <t>incident_reported_by_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option1':_'active',_'label':_'null'}</t>
+          <t>employee_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option1': 'Active', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>incident_status_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'option2':_'inactive',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'option2': 'Inactive', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>incident_status_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'option3':_'pending',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'option3': 'Pending', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>incident_type_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'option1':_'incident_type',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'option1': 'Incident Type', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>incident_type_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'option2':_'other',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'option2': 'Other', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>incident_category_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'option1':_'category_1',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'option1': 'Category 1', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>incident_category_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'option2':_'category_2',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'option2': 'Category 2', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>incident_category_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'option3':_'category_3',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'option3': 'Category 3', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>retail_store_id_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'option1':_'retail_store_1',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'option1': 'Retail Store 1', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>retail_store_id_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'option2':_'retail_store_2',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'option2': 'Retail Store 2', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>retail_store_id_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'option3':_'retail_store_3',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'option3': 'Retail Store 3', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>incident_reported_by_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'option1':_'employee_1',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'option1': 'Employee 1', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>incident_reported_by_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'option2':_'employee_2',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'option2': 'Employee 2', 'label': 'null'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>incident_reported_by_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'option3':_'employee_3',_'label':_'null'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'option3': 'Employee 3', 'label': 'null'}</t>
+          <t>Employee 3</t>
         </is>
       </c>
     </row>
